--- a/data_pipeline_inExcel.xlsx
+++ b/data_pipeline_inExcel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\GitHub_niskin\data_pipeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3895792-FD4C-4828-BD9B-AC5050EFAF2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66AEC450-E2EB-4DA6-A7F2-6C625BDBDB4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27525" yWindow="4155" windowWidth="27495" windowHeight="16290" activeTab="1" xr2:uid="{601F4121-6B15-4DAB-9F8D-B5E17A764040}"/>
+    <workbookView xWindow="-27735" yWindow="4650" windowWidth="27675" windowHeight="15210" xr2:uid="{601F4121-6B15-4DAB-9F8D-B5E17A764040}"/>
   </bookViews>
   <sheets>
     <sheet name="mergedSections" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="24">
   <si>
     <t>at sea</t>
   </si>
@@ -37,30 +37,15 @@
     <t>BATS team: CTD data processing</t>
   </si>
   <si>
-    <t>BATs team: move data to DropBox</t>
-  </si>
-  <si>
     <t>Get R script from github.com/BIOS-SCOPE/data_pipeline/R_code</t>
   </si>
   <si>
     <t>Get MATLAB scripts from github.com/BIOS-SCOPE/data_pipeline/MATLAB_code</t>
   </si>
   <si>
-    <t>Assigned to: Rachel Parsons (or Craig Carlson)</t>
-  </si>
-  <si>
     <t>Transfer data to BIOS-SCOPE Google Drive</t>
   </si>
   <si>
-    <t>Collect water for discrete samples</t>
-  </si>
-  <si>
-    <t>Process discrete samples (in lab)</t>
-  </si>
-  <si>
-    <t>End result: data file for each set of discrete samples</t>
-  </si>
-  <si>
     <t>Generate CTD data</t>
   </si>
   <si>
@@ -119,7 +104,183 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Plan</t>
+      <t>Status</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: generates CSV file with the calculated variables</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Action required</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: the derived variables are copy/pasted into the bottle file</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Status</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: generates a new bottle file with data from discrete samples</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Action required</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: need to update the log in the Excel file with user/date information</t>
+    </r>
+  </si>
+  <si>
+    <t>Join_discreteData_v3.R</t>
+  </si>
+  <si>
+    <t>BATS team: move BIOS-SCOPE data to DropBox; all other data at BCO-DMO</t>
+  </si>
+  <si>
+    <t>Assigned to: Krista Longnecker or Rachel Parson</t>
+  </si>
+  <si>
+    <t>preProcessingCTDfiles.m</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Status</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Reads in CTD data from BCO-DMO and the BIOS-SCOPE only files</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Action required</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: run the script</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Outcome</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: CTD data for all cruises available with one folder/file for each cruise</t>
+    </r>
+  </si>
+  <si>
+    <t>Join_BATS_All_with_master_v5.R</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Future plan</t>
     </r>
     <r>
       <rPr>
@@ -133,6 +294,9 @@
     </r>
   </si>
   <si>
+    <t>calculateDerivedVariables_v1.m</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -142,53 +306,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Status</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: generates CSV file with the calculated variables</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Action required</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: the derived variables are copy/pasted into the bottle file</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Plan</t>
+      <t>Future plan</t>
     </r>
     <r>
       <rPr>
@@ -200,209 +318,13 @@
       </rPr>
       <t>: edit the bottle file to insert the calculated variables automatically</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Status</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: generates a new bottle file with data from discrete samples</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Action required</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: need to update the log in the Excel file with user/date information</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Plan</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: need to see an individual data file</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Status</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: generates one Excel sheet with all the discrete data</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Next step</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: copy the new worksheet into the discrete file, copy the header with the colors, update the log</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Status</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: opens up Excel file with new data in rows</t>
-    </r>
-  </si>
-  <si>
-    <t>Join_BATS_All_with_master_v3.R</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Next step</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: append the new rows to the existing bottle file; update the log; save Excel file with new date</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Next step:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> use Join_discreteData_v2.R to pull the variables into the bottle file</t>
-    </r>
-  </si>
-  <si>
-    <t>Create_bioscope_files_2024_Krista.m</t>
-  </si>
-  <si>
-    <t>Join_discreteData_v3.R</t>
-  </si>
-  <si>
-    <t>Create_biosscope_files_2026.m</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -435,14 +357,6 @@
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -520,7 +434,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
@@ -541,34 +455,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -886,279 +784,297 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="17.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" customWidth="1"/>
     <col min="2" max="2" width="15.140625" customWidth="1"/>
-    <col min="3" max="3" width="106" customWidth="1"/>
+    <col min="3" max="3" width="92.5703125" customWidth="1"/>
     <col min="4" max="4" width="46.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="B1" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="9"/>
+    </row>
+    <row r="2" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="4"/>
-      <c r="D2" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10"/>
+    </row>
+    <row r="3" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="11"/>
       <c r="B3" s="4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C3" s="4"/>
-      <c r="D3" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10"/>
+    </row>
+    <row r="4" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="12"/>
       <c r="B4" s="5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C4" s="4"/>
-      <c r="D4" s="13"/>
-    </row>
-    <row r="5" spans="1:4" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10"/>
-      <c r="B5" s="4"/>
+    </row>
+    <row r="5" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="12"/>
+      <c r="B5" s="8"/>
       <c r="C5" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="13"/>
-    </row>
-    <row r="6" spans="1:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="12"/>
       <c r="B6" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="4"/>
-      <c r="D6" s="13"/>
-    </row>
-    <row r="7" spans="1:4" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10"/>
-      <c r="B7" s="15"/>
+    </row>
+    <row r="7" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="12"/>
+      <c r="B7" s="10"/>
       <c r="C7" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="13"/>
-    </row>
-    <row r="8" spans="1:4" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10"/>
-      <c r="B8" s="16"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="12"/>
+      <c r="B8" s="10"/>
       <c r="C8" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="12"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="12"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="12"/>
+      <c r="B11" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="4"/>
+    </row>
+    <row r="12" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="12"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="12"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="12"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="12"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="12"/>
+      <c r="B16" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="4"/>
+    </row>
+    <row r="17" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="12"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="12"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="12"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="12"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="13"/>
-    </row>
-    <row r="9" spans="1:4" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="13"/>
-    </row>
-    <row r="10" spans="1:4" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10"/>
-      <c r="B10" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="13"/>
-    </row>
-    <row r="11" spans="1:4" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="13"/>
-    </row>
-    <row r="12" spans="1:4" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="13"/>
-    </row>
-    <row r="13" spans="1:4" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="10"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" s="13"/>
-    </row>
-    <row r="14" spans="1:4" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="10"/>
-      <c r="B14" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="13"/>
-    </row>
-    <row r="15" spans="1:4" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="10"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" s="13"/>
-    </row>
-    <row r="16" spans="1:4" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16" s="13"/>
-    </row>
-    <row r="17" spans="1:4" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="11"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" s="14"/>
+    </row>
+    <row r="21" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="12"/>
+      <c r="B21" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21" s="4"/>
+    </row>
+    <row r="22" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="12"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="12"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="13"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="5" t="s">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A2:A17"/>
-    <mergeCell ref="D3:D17"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B15:B17"/>
+  <mergeCells count="6">
+    <mergeCell ref="A3:A24"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="B12:B15"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="B1:C1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="59" orientation="portrait" r:id="rId1"/>
+  <pageSetup scale="75" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC9BB768-0C33-466A-87BD-A91485B7023F}">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" customWidth="1"/>
     <col min="2" max="2" width="15.140625" customWidth="1"/>
-    <col min="3" max="3" width="78" customWidth="1"/>
+    <col min="3" max="3" width="88.7109375" customWidth="1"/>
     <col min="4" max="4" width="46.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C5" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="C8" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C9" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C10" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C11" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C12" s="2"/>
-    </row>
-    <row r="13" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C12" s="1"/>
+    </row>
+    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="C14" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C15" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C16" s="2" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C17" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -1171,23 +1087,49 @@
     </row>
     <row r="20" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="C20" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C21" s="2" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C22" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C23" s="2" t="s">
-        <v>20</v>
-      </c>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C24" s="2"/>
+    </row>
+    <row r="25" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B25" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="C26" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C27" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C28" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C29" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data_pipeline_inExcel.xlsx
+++ b/data_pipeline_inExcel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\GitHub_niskin\data_pipeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66AEC450-E2EB-4DA6-A7F2-6C625BDBDB4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8A31B19-5A64-4F39-8597-ABD94C92B5B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27735" yWindow="4650" windowWidth="27675" windowHeight="15210" xr2:uid="{601F4121-6B15-4DAB-9F8D-B5E17A764040}"/>
+    <workbookView xWindow="1815" yWindow="1305" windowWidth="36180" windowHeight="18840" xr2:uid="{601F4121-6B15-4DAB-9F8D-B5E17A764040}"/>
   </bookViews>
   <sheets>
     <sheet name="mergedSections" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="21">
   <si>
     <t>at sea</t>
   </si>
@@ -114,7 +114,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>: generates CSV file with the calculated variables</t>
+      <t>: generates a new bottle file with data from discrete samples</t>
     </r>
   </si>
   <si>
@@ -137,8 +137,20 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>: the derived variables are copy/pasted into the bottle file</t>
-    </r>
+      <t>: need to update the log in the Excel file with user/date information</t>
+    </r>
+  </si>
+  <si>
+    <t>Join_discreteData_v3.R</t>
+  </si>
+  <si>
+    <t>BATS team: move BIOS-SCOPE data to DropBox; all other data at BCO-DMO</t>
+  </si>
+  <si>
+    <t>Assigned to: Krista Longnecker or Rachel Parson</t>
+  </si>
+  <si>
+    <t>preProcessingCTDfiles.m</t>
   </si>
   <si>
     <r>
@@ -160,7 +172,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>: generates a new bottle file with data from discrete samples</t>
+      <t>: Reads in CTD data from BCO-DMO and the BIOS-SCOPE only files</t>
     </r>
   </si>
   <si>
@@ -183,20 +195,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>: need to update the log in the Excel file with user/date information</t>
-    </r>
-  </si>
-  <si>
-    <t>Join_discreteData_v3.R</t>
-  </si>
-  <si>
-    <t>BATS team: move BIOS-SCOPE data to DropBox; all other data at BCO-DMO</t>
-  </si>
-  <si>
-    <t>Assigned to: Krista Longnecker or Rachel Parson</t>
-  </si>
-  <si>
-    <t>preProcessingCTDfiles.m</t>
+      <t>: run the script</t>
+    </r>
   </si>
   <si>
     <r>
@@ -208,18 +208,21 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Status</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Reads in CTD data from BCO-DMO and the BIOS-SCOPE only files</t>
-    </r>
+      <t>Outcome</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: CTD data for all cruises available with one folder/file for each cruise</t>
+    </r>
+  </si>
+  <si>
+    <t>Join_BATS_All_with_master_v5.R</t>
   </si>
   <si>
     <r>
@@ -231,17 +234,17 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Action required</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: run the script</t>
+      <t>Future plan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: add new rows in a way that automatically saves a new version of the bottle file</t>
     </r>
   </si>
   <si>
@@ -264,59 +267,28 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>: CTD data for all cruises available with one folder/file for each cruise</t>
-    </r>
-  </si>
-  <si>
-    <t>Join_BATS_All_with_master_v5.R</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Future plan</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: add new rows in a way that automatically saves a new version of the bottle file</t>
-    </r>
-  </si>
-  <si>
-    <t>calculateDerivedVariables_v1.m</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Future plan</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: edit the bottle file to insert the calculated variables automatically</t>
+      <t xml:space="preserve">: CTD data for all cruises </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>the derived variables</t>
     </r>
   </si>
 </sst>
@@ -324,7 +296,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -361,6 +333,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -458,15 +438,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -784,7 +764,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="17.45" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" customWidth="1"/>
@@ -797,10 +777,10 @@
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="9"/>
+      <c r="C1" s="13"/>
     </row>
     <row r="2" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -812,167 +792,131 @@
       <c r="C2" s="4"/>
     </row>
     <row r="3" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11"/>
+      <c r="A3" s="9"/>
       <c r="B3" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C3" s="4"/>
     </row>
     <row r="4" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
+      <c r="A4" s="10"/>
       <c r="B4" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="4"/>
     </row>
     <row r="5" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
+      <c r="A5" s="10"/>
       <c r="B5" s="8"/>
       <c r="C5" s="6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
+      <c r="A6" s="10"/>
       <c r="B6" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="4"/>
     </row>
     <row r="7" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="12"/>
-      <c r="B7" s="10"/>
+      <c r="A7" s="10"/>
+      <c r="B7" s="12"/>
       <c r="C7" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="12"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="12"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
     <row r="10" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="12"/>
-      <c r="B10" s="10"/>
+      <c r="A10" s="10"/>
+      <c r="B10" s="12"/>
       <c r="C10" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="12"/>
+      <c r="A11" s="10"/>
       <c r="B11" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C11" s="4"/>
     </row>
     <row r="12" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="12"/>
-      <c r="B12" s="10"/>
+      <c r="A12" s="10"/>
+      <c r="B12" s="12"/>
       <c r="C12" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="12"/>
-      <c r="B13" s="10"/>
+      <c r="A13" s="10"/>
+      <c r="B13" s="12"/>
       <c r="C13" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="12"/>
-      <c r="B14" s="10"/>
+      <c r="A14" s="10"/>
+      <c r="B14" s="12"/>
       <c r="C14" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="12"/>
-      <c r="B15" s="10"/>
+      <c r="A15" s="10"/>
+      <c r="B15" s="12"/>
       <c r="C15" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="12"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="10"/>
       <c r="B16" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16" s="4"/>
     </row>
     <row r="17" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="12"/>
-      <c r="B17" s="10"/>
+      <c r="A17" s="10"/>
+      <c r="B17" s="12"/>
       <c r="C17" s="7" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="12"/>
-      <c r="B18" s="10"/>
+      <c r="A18" s="10"/>
+      <c r="B18" s="12"/>
       <c r="C18" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="12"/>
-      <c r="B19" s="10"/>
+      <c r="A19" s="11"/>
+      <c r="B19" s="12"/>
       <c r="C19" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="12"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="12"/>
-      <c r="B21" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C21" s="4"/>
-    </row>
-    <row r="22" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="12"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="12"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="13"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A3:A24"/>
+  <mergeCells count="5">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="A3:A19"/>
     <mergeCell ref="B7:B10"/>
     <mergeCell ref="B12:B15"/>
-    <mergeCell ref="B17:B20"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="B17:B19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="75" orientation="portrait" r:id="rId1"/>
@@ -981,7 +925,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC9BB768-0C33-466A-87BD-A91485B7023F}">
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" customWidth="1"/>
@@ -1008,7 +952,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -1018,7 +962,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1031,22 +975,22 @@
     </row>
     <row r="8" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="C8" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C9" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C10" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C11" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -1059,7 +1003,7 @@
     </row>
     <row r="14" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="C14" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -1074,7 +1018,7 @@
     </row>
     <row r="17" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C17" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -1082,12 +1026,12 @@
     </row>
     <row r="19" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="C20" s="3" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -1101,35 +1045,7 @@
       </c>
     </row>
     <row r="23" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C23" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C24" s="2"/>
-    </row>
-    <row r="25" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B25" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="C26" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C27" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C28" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C29" s="2"/>
+      <c r="C23" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
